--- a/joy/标点符号漂移方案.xlsx
+++ b/joy/标点符号漂移方案.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="66600" windowWidth="15705" windowHeight="7725" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="67200" windowWidth="15705" windowHeight="7725" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="标点频率统计" sheetId="1" r:id="rId1"/>
@@ -1645,14 +1645,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>左Shift键轮换</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>右Shift键轮换</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>数字时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8957,6 +8949,14 @@
       </rPr>
       <t>➋</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左Win+左Shift 轮换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左Win+右Shift 轮换</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9504,8 +9504,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表3" displayName="表3" ref="A1:C2" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <tableColumns count="3">
     <tableColumn id="1" name="数字时" dataDxfId="2"/>
-    <tableColumn id="2" name="左Shift键轮换" dataDxfId="1"/>
-    <tableColumn id="3" name="右Shift键轮换" dataDxfId="0"/>
+    <tableColumn id="2" name="左Win+左Shift 轮换" dataDxfId="1"/>
+    <tableColumn id="3" name="左Win+右Shift 轮换" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10693,19 +10693,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>81</v>
@@ -10714,13 +10714,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2"/>
@@ -10733,13 +10733,13 @@
         <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>82</v>
@@ -10750,22 +10750,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="G4" t="s">
         <v>92</v>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>57</v>
@@ -10785,7 +10785,7 @@
         <v>52</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>83</v>
@@ -10796,19 +10796,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>84</v>
@@ -10823,34 +10823,34 @@
         <v>65</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>85</v>
@@ -10867,10 +10867,10 @@
         <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>75</v>
@@ -10885,16 +10885,16 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G10" t="s">
         <v>94</v>
@@ -10902,22 +10902,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G11"/>
     </row>
@@ -10932,10 +10932,10 @@
         <v>48</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>72</v>
@@ -10952,13 +10952,13 @@
         <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>73</v>
@@ -10969,22 +10969,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="G14" t="s">
         <v>93</v>
@@ -10998,16 +10998,16 @@
         <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G15"/>
     </row>
@@ -11025,7 +11025,7 @@
         <v>48</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -11034,19 +11034,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -11055,16 +11055,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>76</v>
@@ -11079,16 +11079,16 @@
         <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
         <v>91</v>
@@ -11102,16 +11102,16 @@
         <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G20" t="s">
         <v>91</v>
@@ -11119,10 +11119,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>48</v>
@@ -11131,28 +11131,28 @@
         <v>48</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G21"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
@@ -11161,22 +11161,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G23" t="s">
         <v>54</v>
@@ -11190,16 +11190,16 @@
         <v>38</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G24"/>
     </row>
@@ -11211,16 +11211,16 @@
         <v>39</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G25" t="s">
         <v>97</v>
@@ -11228,19 +11228,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>86</v>
@@ -11251,19 +11251,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -11278,13 +11278,13 @@
         <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
@@ -11299,37 +11299,37 @@
         <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G29"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G30" t="s">
         <v>98</v>
@@ -11337,22 +11337,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G31" t="s">
         <v>99</v>
@@ -11360,22 +11360,22 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G32" t="s">
         <v>97</v>
@@ -11389,16 +11389,16 @@
         <v>49</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -11412,16 +11412,16 @@
         <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G34" t="s">
         <v>95</v>
@@ -11429,7 +11429,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
@@ -11453,18 +11453,18 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="20.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>102</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.2">
@@ -11472,10 +11472,10 @@
         <v>100</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
